--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23536,10 +23536,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113188753</v>
+        <v>113188751</v>
       </c>
       <c r="B204" t="n">
-        <v>56872</v>
+        <v>98564</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23552,43 +23552,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103031</v>
+        <v>2082</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>538060</v>
+        <v>538063</v>
       </c>
       <c r="R204" t="n">
-        <v>7202697</v>
+        <v>7202681</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -23620,7 +23611,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23630,7 +23621,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23657,10 +23648,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113188751</v>
+        <v>113188753</v>
       </c>
       <c r="B205" t="n">
-        <v>98548</v>
+        <v>56872</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23673,34 +23664,43 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2082</v>
+        <v>103031</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>538063</v>
+        <v>538060</v>
       </c>
       <c r="R205" t="n">
-        <v>7202681</v>
+        <v>7202697</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98548</v>
+        <v>98564</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23536,10 +23536,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113188751</v>
+        <v>113188753</v>
       </c>
       <c r="B204" t="n">
-        <v>98564</v>
+        <v>56872</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23552,34 +23552,43 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2082</v>
+        <v>103031</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>538063</v>
+        <v>538060</v>
       </c>
       <c r="R204" t="n">
-        <v>7202681</v>
+        <v>7202697</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -23611,7 +23620,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23621,7 +23630,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23648,10 +23657,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113188753</v>
+        <v>113188751</v>
       </c>
       <c r="B205" t="n">
-        <v>56872</v>
+        <v>98564</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23664,43 +23673,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103031</v>
+        <v>2082</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>538060</v>
+        <v>538063</v>
       </c>
       <c r="R205" t="n">
-        <v>7202697</v>
+        <v>7202681</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD205" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23536,10 +23536,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113188753</v>
+        <v>113188751</v>
       </c>
       <c r="B204" t="n">
-        <v>56872</v>
+        <v>98576</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23552,43 +23552,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103031</v>
+        <v>2082</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>538060</v>
+        <v>538063</v>
       </c>
       <c r="R204" t="n">
-        <v>7202697</v>
+        <v>7202681</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -23620,7 +23611,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23630,7 +23621,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23657,10 +23648,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113188751</v>
+        <v>113188753</v>
       </c>
       <c r="B205" t="n">
-        <v>98564</v>
+        <v>56873</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23673,34 +23664,43 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2082</v>
+        <v>103031</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>538063</v>
+        <v>538060</v>
       </c>
       <c r="R205" t="n">
-        <v>7202681</v>
+        <v>7202697</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98564</v>
+        <v>98576</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23536,10 +23536,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113188751</v>
+        <v>113188753</v>
       </c>
       <c r="B204" t="n">
-        <v>98576</v>
+        <v>56873</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23552,34 +23552,43 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2082</v>
+        <v>103031</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>538063</v>
+        <v>538060</v>
       </c>
       <c r="R204" t="n">
-        <v>7202681</v>
+        <v>7202697</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -23611,7 +23620,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23621,7 +23630,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23648,10 +23657,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113188753</v>
+        <v>113188751</v>
       </c>
       <c r="B205" t="n">
-        <v>56873</v>
+        <v>98576</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23664,43 +23673,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103031</v>
+        <v>2082</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>538060</v>
+        <v>538063</v>
       </c>
       <c r="R205" t="n">
-        <v>7202697</v>
+        <v>7202681</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD205" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23660,7 +23660,7 @@
         <v>113188751</v>
       </c>
       <c r="B205" t="n">
-        <v>98576</v>
+        <v>98598</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98576</v>
+        <v>98598</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23539,7 +23539,7 @@
         <v>113188753</v>
       </c>
       <c r="B204" t="n">
-        <v>56873</v>
+        <v>56876</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>113188751</v>
       </c>
       <c r="B205" t="n">
-        <v>98598</v>
+        <v>98602</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98598</v>
+        <v>98602</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23536,10 +23536,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113188753</v>
+        <v>113188751</v>
       </c>
       <c r="B204" t="n">
-        <v>56876</v>
+        <v>98608</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -23552,43 +23552,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>103031</v>
+        <v>2082</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>538060</v>
+        <v>538063</v>
       </c>
       <c r="R204" t="n">
-        <v>7202697</v>
+        <v>7202681</v>
       </c>
       <c r="S204" t="n">
         <v>25</v>
@@ -23620,7 +23611,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -23630,7 +23621,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23657,10 +23648,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113188751</v>
+        <v>113188753</v>
       </c>
       <c r="B205" t="n">
-        <v>98602</v>
+        <v>56880</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -23673,34 +23664,43 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2082</v>
+        <v>103031</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>538063</v>
+        <v>538060</v>
       </c>
       <c r="R205" t="n">
-        <v>7202681</v>
+        <v>7202697</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD205" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98602</v>
+        <v>98608</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98608</v>
+        <v>98615</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -23772,7 +23772,7 @@
         <v>113334415</v>
       </c>
       <c r="B206" t="n">
-        <v>98615</v>
+        <v>98620</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY238"/>
+  <dimension ref="A1:AY240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27203,6 +27203,233 @@
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>114731504</v>
+      </c>
+      <c r="B239" t="n">
+        <v>98780</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Lill-Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>538141</v>
+      </c>
+      <c r="R239" t="n">
+        <v>7202587</v>
+      </c>
+      <c r="S239" t="n">
+        <v>20</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>AC-Vil-0226</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF239" t="inlineStr"/>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Sandra Sundkvist, Noomi Berg, Tommy Manfredsson</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>114731498</v>
+      </c>
+      <c r="B240" t="n">
+        <v>98780</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>538691</v>
+      </c>
+      <c r="R240" t="n">
+        <v>7202672</v>
+      </c>
+      <c r="S240" t="n">
+        <v>25</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>AC-Vil-0229</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY240"/>
+  <dimension ref="A1:AY250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27437,6 +27437,1135 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>120461289</v>
+      </c>
+      <c r="B241" t="n">
+        <v>79570</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>1153</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Olivbrun gytterlav</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Fuscopannaria mediterranea</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>(Tav.) P.M.Jørg.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>538104</v>
+      </c>
+      <c r="R241" t="n">
+        <v>7202604</v>
+      </c>
+      <c r="S241" t="n">
+        <v>25</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>120461305</v>
+      </c>
+      <c r="B242" t="n">
+        <v>79668</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>538061</v>
+      </c>
+      <c r="R242" t="n">
+        <v>7202687</v>
+      </c>
+      <c r="S242" t="n">
+        <v>25</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>120461297</v>
+      </c>
+      <c r="B243" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>537963</v>
+      </c>
+      <c r="R243" t="n">
+        <v>7202681</v>
+      </c>
+      <c r="S243" t="n">
+        <v>25</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>120461307</v>
+      </c>
+      <c r="B244" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>538061</v>
+      </c>
+      <c r="R244" t="n">
+        <v>7202713</v>
+      </c>
+      <c r="S244" t="n">
+        <v>25</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>120461298</v>
+      </c>
+      <c r="B245" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>658</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>537964</v>
+      </c>
+      <c r="R245" t="n">
+        <v>7202678</v>
+      </c>
+      <c r="S245" t="n">
+        <v>25</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>120461300</v>
+      </c>
+      <c r="B246" t="n">
+        <v>79668</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>537966</v>
+      </c>
+      <c r="R246" t="n">
+        <v>7202674</v>
+      </c>
+      <c r="S246" t="n">
+        <v>25</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>120461308</v>
+      </c>
+      <c r="B247" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>538071</v>
+      </c>
+      <c r="R247" t="n">
+        <v>7202684</v>
+      </c>
+      <c r="S247" t="n">
+        <v>25</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>120461310</v>
+      </c>
+      <c r="B248" t="n">
+        <v>93762</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>538133</v>
+      </c>
+      <c r="R248" t="n">
+        <v>7202570</v>
+      </c>
+      <c r="S248" t="n">
+        <v>25</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>120461299</v>
+      </c>
+      <c r="B249" t="n">
+        <v>79583</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>537966</v>
+      </c>
+      <c r="R249" t="n">
+        <v>7202674</v>
+      </c>
+      <c r="S249" t="n">
+        <v>25</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>120461301</v>
+      </c>
+      <c r="B250" t="n">
+        <v>79570</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>1153</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Olivbrun gytterlav</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Fuscopannaria mediterranea</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Tav.) P.M.Jørg.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>537962</v>
+      </c>
+      <c r="R250" t="n">
+        <v>7202677</v>
+      </c>
+      <c r="S250" t="n">
+        <v>25</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -27439,10 +27439,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120461289</v>
+        <v>120461307</v>
       </c>
       <c r="B241" t="n">
-        <v>79570</v>
+        <v>57320</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27455,34 +27455,43 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1153</v>
+        <v>100109</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>538104</v>
+        <v>538061</v>
       </c>
       <c r="R241" t="n">
-        <v>7202604</v>
+        <v>7202713</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -27514,7 +27523,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27524,7 +27533,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27551,10 +27560,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120461305</v>
+        <v>120461301</v>
       </c>
       <c r="B242" t="n">
-        <v>79668</v>
+        <v>79570</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27567,21 +27576,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>229504</v>
+        <v>1153</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27591,10 +27600,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>538061</v>
+        <v>537962</v>
       </c>
       <c r="R242" t="n">
-        <v>7202687</v>
+        <v>7202677</v>
       </c>
       <c r="S242" t="n">
         <v>25</v>
@@ -27626,7 +27635,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27636,7 +27645,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27663,10 +27672,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120461297</v>
+        <v>120461300</v>
       </c>
       <c r="B243" t="n">
-        <v>90580</v>
+        <v>79668</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27679,21 +27688,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1202</v>
+        <v>229504</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27703,10 +27712,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537963</v>
+        <v>537966</v>
       </c>
       <c r="R243" t="n">
-        <v>7202681</v>
+        <v>7202674</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -27738,7 +27747,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27748,7 +27757,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27775,10 +27784,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120461307</v>
+        <v>120461310</v>
       </c>
       <c r="B244" t="n">
-        <v>57320</v>
+        <v>93762</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27787,47 +27796,38 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100109</v>
+        <v>1004672</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>538061</v>
+        <v>538133</v>
       </c>
       <c r="R244" t="n">
-        <v>7202713</v>
+        <v>7202570</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27859,7 +27859,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27869,7 +27869,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27896,10 +27896,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120461298</v>
+        <v>120461305</v>
       </c>
       <c r="B245" t="n">
-        <v>90864</v>
+        <v>79668</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27912,21 +27912,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>658</v>
+        <v>229504</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27936,10 +27936,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537964</v>
+        <v>538061</v>
       </c>
       <c r="R245" t="n">
-        <v>7202678</v>
+        <v>7202687</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28008,10 +28008,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120461300</v>
+        <v>120461308</v>
       </c>
       <c r="B246" t="n">
-        <v>79668</v>
+        <v>91512</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28020,25 +28020,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>229504</v>
+        <v>4769</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28048,10 +28048,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537966</v>
+        <v>538071</v>
       </c>
       <c r="R246" t="n">
-        <v>7202674</v>
+        <v>7202684</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28083,7 +28083,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28120,10 +28120,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120461308</v>
+        <v>120461297</v>
       </c>
       <c r="B247" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28132,25 +28132,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28160,10 +28160,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>538071</v>
+        <v>537963</v>
       </c>
       <c r="R247" t="n">
-        <v>7202684</v>
+        <v>7202681</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -28195,7 +28195,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28205,7 +28205,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28232,10 +28232,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120461310</v>
+        <v>120461299</v>
       </c>
       <c r="B248" t="n">
-        <v>93762</v>
+        <v>79583</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28248,21 +28248,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1004672</v>
+        <v>229497</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -28272,10 +28272,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>538133</v>
+        <v>537966</v>
       </c>
       <c r="R248" t="n">
-        <v>7202570</v>
+        <v>7202674</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28307,7 +28307,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28344,10 +28344,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120461299</v>
+        <v>120461289</v>
       </c>
       <c r="B249" t="n">
-        <v>79583</v>
+        <v>79570</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28356,25 +28356,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>229497</v>
+        <v>1153</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28384,10 +28384,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>537966</v>
+        <v>538104</v>
       </c>
       <c r="R249" t="n">
-        <v>7202674</v>
+        <v>7202604</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28419,7 +28419,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28429,7 +28429,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28456,10 +28456,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120461301</v>
+        <v>120461298</v>
       </c>
       <c r="B250" t="n">
-        <v>79570</v>
+        <v>90864</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28472,21 +28472,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1153</v>
+        <v>658</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28496,10 +28496,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>537962</v>
+        <v>537964</v>
       </c>
       <c r="R250" t="n">
-        <v>7202677</v>
+        <v>7202678</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD250" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -27439,10 +27439,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120461307</v>
+        <v>120461301</v>
       </c>
       <c r="B241" t="n">
-        <v>57320</v>
+        <v>79570</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27455,43 +27455,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100109</v>
+        <v>1153</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Tav.) P.M.Jørg.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>538061</v>
+        <v>537962</v>
       </c>
       <c r="R241" t="n">
-        <v>7202713</v>
+        <v>7202677</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -27523,7 +27514,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27533,7 +27524,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27560,10 +27551,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120461301</v>
+        <v>120461299</v>
       </c>
       <c r="B242" t="n">
-        <v>79570</v>
+        <v>79583</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27572,25 +27563,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1153</v>
+        <v>229497</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27600,10 +27591,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537962</v>
+        <v>537966</v>
       </c>
       <c r="R242" t="n">
-        <v>7202677</v>
+        <v>7202674</v>
       </c>
       <c r="S242" t="n">
         <v>25</v>
@@ -27635,7 +27626,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27645,7 +27636,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27784,10 +27775,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120461310</v>
+        <v>120461297</v>
       </c>
       <c r="B244" t="n">
-        <v>93762</v>
+        <v>90580</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27796,25 +27787,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1004672</v>
+        <v>1202</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27824,10 +27815,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>538133</v>
+        <v>537963</v>
       </c>
       <c r="R244" t="n">
-        <v>7202570</v>
+        <v>7202681</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27859,7 +27850,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27869,7 +27860,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27896,10 +27887,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120461305</v>
+        <v>120461310</v>
       </c>
       <c r="B245" t="n">
-        <v>79668</v>
+        <v>93762</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27908,25 +27899,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>229504</v>
+        <v>1004672</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27936,10 +27927,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>538061</v>
+        <v>538133</v>
       </c>
       <c r="R245" t="n">
-        <v>7202687</v>
+        <v>7202570</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27971,7 +27962,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27981,7 +27972,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28008,10 +27999,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120461308</v>
+        <v>120461305</v>
       </c>
       <c r="B246" t="n">
-        <v>91512</v>
+        <v>79668</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28020,25 +28011,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4769</v>
+        <v>229504</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28048,10 +28039,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>538071</v>
+        <v>538061</v>
       </c>
       <c r="R246" t="n">
-        <v>7202684</v>
+        <v>7202687</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28083,7 +28074,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28093,7 +28084,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28120,10 +28111,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120461297</v>
+        <v>120461298</v>
       </c>
       <c r="B247" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28136,21 +28127,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28160,10 +28151,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537963</v>
+        <v>537964</v>
       </c>
       <c r="R247" t="n">
-        <v>7202681</v>
+        <v>7202678</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -28232,10 +28223,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120461299</v>
+        <v>120461307</v>
       </c>
       <c r="B248" t="n">
-        <v>79583</v>
+        <v>57320</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28244,38 +28235,47 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P248" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537966</v>
+        <v>538061</v>
       </c>
       <c r="R248" t="n">
-        <v>7202674</v>
+        <v>7202713</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28307,7 +28307,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28317,7 +28317,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28344,10 +28344,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120461289</v>
+        <v>120461308</v>
       </c>
       <c r="B249" t="n">
-        <v>79570</v>
+        <v>91512</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28356,25 +28356,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1153</v>
+        <v>4769</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28384,10 +28384,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>538104</v>
+        <v>538071</v>
       </c>
       <c r="R249" t="n">
-        <v>7202604</v>
+        <v>7202684</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28419,7 +28419,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28429,7 +28429,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28456,10 +28456,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120461298</v>
+        <v>120461289</v>
       </c>
       <c r="B250" t="n">
-        <v>90864</v>
+        <v>79570</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28472,21 +28472,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>658</v>
+        <v>1153</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28496,10 +28496,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>537964</v>
+        <v>538104</v>
       </c>
       <c r="R250" t="n">
-        <v>7202678</v>
+        <v>7202604</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD250" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -27439,10 +27439,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120461301</v>
+        <v>120461305</v>
       </c>
       <c r="B241" t="n">
-        <v>79570</v>
+        <v>79668</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27455,21 +27455,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1153</v>
+        <v>229504</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27479,10 +27479,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537962</v>
+        <v>538061</v>
       </c>
       <c r="R241" t="n">
-        <v>7202677</v>
+        <v>7202687</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27551,10 +27551,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120461299</v>
+        <v>120461300</v>
       </c>
       <c r="B242" t="n">
-        <v>79583</v>
+        <v>79668</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27563,25 +27563,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>229497</v>
+        <v>229504</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27663,10 +27663,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120461300</v>
+        <v>120461289</v>
       </c>
       <c r="B243" t="n">
-        <v>79668</v>
+        <v>79570</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27679,21 +27679,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>229504</v>
+        <v>1153</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27703,10 +27703,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537966</v>
+        <v>538104</v>
       </c>
       <c r="R243" t="n">
-        <v>7202674</v>
+        <v>7202604</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -27738,7 +27738,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27775,10 +27775,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120461297</v>
+        <v>120461299</v>
       </c>
       <c r="B244" t="n">
-        <v>90580</v>
+        <v>79583</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27787,25 +27787,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27815,10 +27815,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537963</v>
+        <v>537966</v>
       </c>
       <c r="R244" t="n">
-        <v>7202681</v>
+        <v>7202674</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27850,7 +27850,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27887,10 +27887,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120461310</v>
+        <v>120461301</v>
       </c>
       <c r="B245" t="n">
-        <v>93762</v>
+        <v>79570</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27899,25 +27899,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1004672</v>
+        <v>1153</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27927,10 +27927,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>538133</v>
+        <v>537962</v>
       </c>
       <c r="R245" t="n">
-        <v>7202570</v>
+        <v>7202677</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27999,10 +27999,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120461305</v>
+        <v>120461298</v>
       </c>
       <c r="B246" t="n">
-        <v>79668</v>
+        <v>90864</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28015,21 +28015,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>229504</v>
+        <v>658</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28039,10 +28039,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>538061</v>
+        <v>537964</v>
       </c>
       <c r="R246" t="n">
-        <v>7202687</v>
+        <v>7202678</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28074,7 +28074,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28111,10 +28111,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120461298</v>
+        <v>120461308</v>
       </c>
       <c r="B247" t="n">
-        <v>90864</v>
+        <v>91512</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28123,25 +28123,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28151,10 +28151,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537964</v>
+        <v>538071</v>
       </c>
       <c r="R247" t="n">
-        <v>7202678</v>
+        <v>7202684</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -28186,7 +28186,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28223,10 +28223,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120461307</v>
+        <v>120461310</v>
       </c>
       <c r="B248" t="n">
-        <v>57320</v>
+        <v>93762</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28235,47 +28235,38 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>100109</v>
+        <v>1004672</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>538061</v>
+        <v>538133</v>
       </c>
       <c r="R248" t="n">
-        <v>7202713</v>
+        <v>7202570</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28307,7 +28298,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28317,7 +28308,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28344,10 +28335,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120461308</v>
+        <v>120461307</v>
       </c>
       <c r="B249" t="n">
-        <v>91512</v>
+        <v>57320</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28356,38 +28347,47 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P249" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>538071</v>
+        <v>538061</v>
       </c>
       <c r="R249" t="n">
-        <v>7202684</v>
+        <v>7202713</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28419,7 +28419,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28429,7 +28429,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28456,10 +28456,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120461289</v>
+        <v>120461297</v>
       </c>
       <c r="B250" t="n">
-        <v>79570</v>
+        <v>90580</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28472,21 +28472,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1153</v>
+        <v>1202</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28496,10 +28496,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>538104</v>
+        <v>537963</v>
       </c>
       <c r="R250" t="n">
-        <v>7202604</v>
+        <v>7202681</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD250" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -27439,10 +27439,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120461305</v>
+        <v>120461308</v>
       </c>
       <c r="B241" t="n">
-        <v>79668</v>
+        <v>91512</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27451,25 +27451,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>229504</v>
+        <v>4769</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27479,10 +27479,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>538061</v>
+        <v>538071</v>
       </c>
       <c r="R241" t="n">
-        <v>7202687</v>
+        <v>7202684</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27663,10 +27663,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120461289</v>
+        <v>120461298</v>
       </c>
       <c r="B243" t="n">
-        <v>79570</v>
+        <v>90864</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27679,21 +27679,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1153</v>
+        <v>658</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27703,10 +27703,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>538104</v>
+        <v>537964</v>
       </c>
       <c r="R243" t="n">
-        <v>7202604</v>
+        <v>7202678</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -27738,7 +27738,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27999,10 +27999,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120461298</v>
+        <v>120461310</v>
       </c>
       <c r="B246" t="n">
-        <v>90864</v>
+        <v>93762</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28011,25 +28011,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>658</v>
+        <v>1004672</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28039,10 +28039,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537964</v>
+        <v>538133</v>
       </c>
       <c r="R246" t="n">
-        <v>7202678</v>
+        <v>7202570</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28074,7 +28074,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28111,10 +28111,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120461308</v>
+        <v>120461305</v>
       </c>
       <c r="B247" t="n">
-        <v>91512</v>
+        <v>79668</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28123,25 +28123,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4769</v>
+        <v>229504</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28151,10 +28151,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>538071</v>
+        <v>538061</v>
       </c>
       <c r="R247" t="n">
-        <v>7202684</v>
+        <v>7202687</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -28186,7 +28186,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28223,10 +28223,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120461310</v>
+        <v>120461297</v>
       </c>
       <c r="B248" t="n">
-        <v>93762</v>
+        <v>90580</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28235,25 +28235,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1004672</v>
+        <v>1202</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -28263,10 +28263,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>538133</v>
+        <v>537963</v>
       </c>
       <c r="R248" t="n">
-        <v>7202570</v>
+        <v>7202681</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28298,7 +28298,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28456,10 +28456,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120461297</v>
+        <v>120461289</v>
       </c>
       <c r="B250" t="n">
-        <v>90580</v>
+        <v>79570</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28472,21 +28472,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1202</v>
+        <v>1153</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28496,10 +28496,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>537963</v>
+        <v>538104</v>
       </c>
       <c r="R250" t="n">
-        <v>7202681</v>
+        <v>7202604</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD250" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -27887,10 +27887,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120461301</v>
+        <v>120461310</v>
       </c>
       <c r="B245" t="n">
-        <v>79570</v>
+        <v>93762</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27899,25 +27899,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1153</v>
+        <v>1004672</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27927,10 +27927,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537962</v>
+        <v>538133</v>
       </c>
       <c r="R245" t="n">
-        <v>7202677</v>
+        <v>7202570</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27999,10 +27999,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120461310</v>
+        <v>120461301</v>
       </c>
       <c r="B246" t="n">
-        <v>93762</v>
+        <v>79570</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28011,25 +28011,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1004672</v>
+        <v>1153</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28039,10 +28039,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>538133</v>
+        <v>537962</v>
       </c>
       <c r="R246" t="n">
-        <v>7202570</v>
+        <v>7202677</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28074,7 +28074,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD246" t="b">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY250"/>
+  <dimension ref="A1:AY251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28566,6 +28566,123 @@
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>122037273</v>
+      </c>
+      <c r="B251" t="n">
+        <v>79657</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1153</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Olivbrun gytterlav</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Fuscopannaria mediterranea</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(Tav.) P.M.Jørg.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Lill-Stalonberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>537964</v>
+      </c>
+      <c r="R251" t="n">
+        <v>7202675</v>
+      </c>
+      <c r="S251" t="n">
+        <v>20</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein, Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28571,7 +28571,7 @@
         <v>122037273</v>
       </c>
       <c r="B251" t="n">
-        <v>79657</v>
+        <v>79659</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28571,7 +28571,7 @@
         <v>122037273</v>
       </c>
       <c r="B251" t="n">
-        <v>79659</v>
+        <v>79660</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28571,7 +28571,7 @@
         <v>122037273</v>
       </c>
       <c r="B251" t="n">
-        <v>79660</v>
+        <v>79667</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28571,7 +28571,7 @@
         <v>122037273</v>
       </c>
       <c r="B251" t="n">
-        <v>79673</v>
+        <v>79674</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28678,7 +28678,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28571,7 +28571,7 @@
         <v>122037273</v>
       </c>
       <c r="B251" t="n">
-        <v>79674</v>
+        <v>79679</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY251"/>
+  <dimension ref="A1:AY250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27101,7 +27101,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>114731504</v>
+        <v>114731472</v>
       </c>
       <c r="B238" t="n">
         <v>98902</v>
@@ -27135,23 +27135,19 @@
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Lill-Stalon, Ås lm</t>
+          <t>Lill-Stalonbergets sydsida, Ås lm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>538141</v>
+        <v>537944</v>
       </c>
       <c r="R238" t="n">
-        <v>7202587</v>
+        <v>7202559</v>
       </c>
       <c r="S238" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27175,17 +27171,17 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>AC-Vil-0226</t>
+          <t>AC-Vil-0018</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27194,7 +27190,6 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
-      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
@@ -27206,7 +27201,7 @@
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Sandra Sundkvist, Noomi Berg, Tommy Manfredsson</t>
+          <t>Isak Vahlström, Martin Westberg</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -27217,7 +27212,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>114731472</v>
+        <v>114731480</v>
       </c>
       <c r="B239" t="n">
         <v>98902</v>
@@ -27253,17 +27248,17 @@
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Lill-Stalonbergets sydsida, Ås lm</t>
+          <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537944</v>
+        <v>538245</v>
       </c>
       <c r="R239" t="n">
-        <v>7202559</v>
+        <v>7202618</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27287,17 +27282,17 @@
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>AC-Vil-0018</t>
+          <t>AC-Vil-0023</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27317,7 +27312,7 @@
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Martin Westberg</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -27328,37 +27323,37 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>114731480</v>
+        <v>120461297</v>
       </c>
       <c r="B240" t="n">
-        <v>98902</v>
+        <v>90670</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>2082</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -27368,10 +27363,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>538245</v>
+        <v>537963</v>
       </c>
       <c r="R240" t="n">
-        <v>7202618</v>
+        <v>7202681</v>
       </c>
       <c r="S240" t="n">
         <v>25</v>
@@ -27396,19 +27391,24 @@
           <t>Vilhelmina</t>
         </is>
       </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>AC-Vil-0023</t>
-        </is>
-      </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27423,26 +27423,22 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY240" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120461297</v>
+        <v>120461289</v>
       </c>
       <c r="B241" t="n">
-        <v>90670</v>
+        <v>79618</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27455,21 +27451,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1202</v>
+        <v>1153</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27479,10 +27475,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537963</v>
+        <v>538104</v>
       </c>
       <c r="R241" t="n">
-        <v>7202681</v>
+        <v>7202604</v>
       </c>
       <c r="S241" t="n">
         <v>25</v>
@@ -27514,7 +27510,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27524,7 +27520,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27551,10 +27547,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120461289</v>
+        <v>120461299</v>
       </c>
       <c r="B242" t="n">
-        <v>79618</v>
+        <v>79631</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27563,25 +27559,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1153</v>
+        <v>229497</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27591,10 +27587,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>538104</v>
+        <v>537966</v>
       </c>
       <c r="R242" t="n">
-        <v>7202604</v>
+        <v>7202674</v>
       </c>
       <c r="S242" t="n">
         <v>25</v>
@@ -27626,7 +27622,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27636,7 +27632,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27663,10 +27659,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120461299</v>
+        <v>120461308</v>
       </c>
       <c r="B243" t="n">
-        <v>79631</v>
+        <v>91602</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27679,21 +27675,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -27703,10 +27699,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537966</v>
+        <v>538071</v>
       </c>
       <c r="R243" t="n">
-        <v>7202674</v>
+        <v>7202684</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -27738,7 +27734,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27748,7 +27744,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27775,10 +27771,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120461308</v>
+        <v>120461307</v>
       </c>
       <c r="B244" t="n">
-        <v>91602</v>
+        <v>57344</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27787,38 +27783,47 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>538071</v>
+        <v>538061</v>
       </c>
       <c r="R244" t="n">
-        <v>7202684</v>
+        <v>7202713</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27850,7 +27855,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27860,7 +27865,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27887,10 +27892,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120461307</v>
+        <v>120461310</v>
       </c>
       <c r="B245" t="n">
-        <v>57344</v>
+        <v>93871</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27899,47 +27904,38 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100109</v>
+        <v>1004672</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Lill-Stalonberget, Ås lm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>538061</v>
+        <v>538133</v>
       </c>
       <c r="R245" t="n">
-        <v>7202713</v>
+        <v>7202570</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27971,7 +27967,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27981,7 +27977,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -28008,10 +28004,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120461310</v>
+        <v>120461300</v>
       </c>
       <c r="B246" t="n">
-        <v>93871</v>
+        <v>79716</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28020,25 +28016,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1004672</v>
+        <v>229504</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -28048,10 +28044,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>538133</v>
+        <v>537966</v>
       </c>
       <c r="R246" t="n">
-        <v>7202570</v>
+        <v>7202674</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -28083,7 +28079,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28093,7 +28089,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28120,10 +28116,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120461300</v>
+        <v>120461298</v>
       </c>
       <c r="B247" t="n">
-        <v>79716</v>
+        <v>90958</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28136,21 +28132,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>229504</v>
+        <v>658</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28160,10 +28156,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537966</v>
+        <v>537964</v>
       </c>
       <c r="R247" t="n">
-        <v>7202674</v>
+        <v>7202678</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -28195,7 +28191,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28205,7 +28201,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28232,10 +28228,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120461298</v>
+        <v>120461301</v>
       </c>
       <c r="B248" t="n">
-        <v>90958</v>
+        <v>79618</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28248,21 +28244,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>658</v>
+        <v>1153</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -28272,10 +28268,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537964</v>
+        <v>537962</v>
       </c>
       <c r="R248" t="n">
-        <v>7202678</v>
+        <v>7202677</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28307,7 +28303,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28317,7 +28313,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28344,10 +28340,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120461301</v>
+        <v>120461305</v>
       </c>
       <c r="B249" t="n">
-        <v>79618</v>
+        <v>79716</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28360,21 +28356,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1153</v>
+        <v>229504</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Olivbrun gytterlav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Fuscopannaria mediterranea</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Tav.) P.M.Jørg.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28384,10 +28380,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>537962</v>
+        <v>538061</v>
       </c>
       <c r="R249" t="n">
-        <v>7202677</v>
+        <v>7202687</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28419,7 +28415,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28429,7 +28425,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28456,10 +28452,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120461305</v>
+        <v>122037273</v>
       </c>
       <c r="B250" t="n">
-        <v>79716</v>
+        <v>79679</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28472,21 +28468,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>229504</v>
+        <v>1153</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Olivbrun gytterlav</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Fuscopannaria mediterranea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Tav.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28496,13 +28492,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>538061</v>
+        <v>537964</v>
       </c>
       <c r="R250" t="n">
-        <v>7202687</v>
+        <v>7202675</v>
       </c>
       <c r="S250" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -28529,21 +28525,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
@@ -28552,136 +28538,34 @@
       </c>
       <c r="AG250" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>122037273</v>
-      </c>
-      <c r="B251" t="n">
-        <v>79679</v>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E251" t="n">
-        <v>1153</v>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Olivbrun gytterlav</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Fuscopannaria mediterranea</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>(Tav.) P.M.Jørg.</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>Lill-Stalonberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q251" t="n">
-        <v>537964</v>
-      </c>
-      <c r="R251" t="n">
-        <v>7202675</v>
-      </c>
-      <c r="S251" t="n">
-        <v>20</v>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AD251" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE251" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG251" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT251" t="inlineStr"/>
-      <c r="AW251" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AX251" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AY251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY250"/>
+  <dimension ref="A1:AY251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28567,6 +28567,122 @@
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>128823092</v>
+      </c>
+      <c r="B251" t="n">
+        <v>91695</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>48</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Handsktumselet, Handsktumselet, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>538092</v>
+      </c>
+      <c r="R251" t="n">
+        <v>7202625</v>
+      </c>
+      <c r="S251" t="n">
+        <v>9</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Lina Albertsen</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Lina Albertsen</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY251"/>
+  <dimension ref="A1:AY264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91695</v>
+        <v>91700</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28682,6 +28682,1357 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>128891095</v>
+      </c>
+      <c r="B252" t="n">
+        <v>86935</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>538049</v>
+      </c>
+      <c r="R252" t="n">
+        <v>7202585</v>
+      </c>
+      <c r="S252" t="n">
+        <v>10</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>128891085</v>
+      </c>
+      <c r="B253" t="n">
+        <v>96871</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>53</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>538126</v>
+      </c>
+      <c r="R253" t="n">
+        <v>7202737</v>
+      </c>
+      <c r="S253" t="n">
+        <v>10</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>128891094</v>
+      </c>
+      <c r="B254" t="n">
+        <v>92434</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>538051</v>
+      </c>
+      <c r="R254" t="n">
+        <v>7202590</v>
+      </c>
+      <c r="S254" t="n">
+        <v>10</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>128891088</v>
+      </c>
+      <c r="B255" t="n">
+        <v>80185</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>538083</v>
+      </c>
+      <c r="R255" t="n">
+        <v>7202660</v>
+      </c>
+      <c r="S255" t="n">
+        <v>10</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>128891096</v>
+      </c>
+      <c r="B256" t="n">
+        <v>91953</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>538050</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7202585</v>
+      </c>
+      <c r="S256" t="n">
+        <v>10</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>128891092</v>
+      </c>
+      <c r="B257" t="n">
+        <v>100719</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>537853</v>
+      </c>
+      <c r="R257" t="n">
+        <v>7202655</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>128891097</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>658</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>538053</v>
+      </c>
+      <c r="R258" t="n">
+        <v>7202582</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>128891099</v>
+      </c>
+      <c r="B259" t="n">
+        <v>90929</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>538171</v>
+      </c>
+      <c r="R259" t="n">
+        <v>7202593</v>
+      </c>
+      <c r="S259" t="n">
+        <v>10</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>128891086</v>
+      </c>
+      <c r="B260" t="n">
+        <v>92434</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>538068</v>
+      </c>
+      <c r="R260" t="n">
+        <v>7202654</v>
+      </c>
+      <c r="S260" t="n">
+        <v>10</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>128891098</v>
+      </c>
+      <c r="B261" t="n">
+        <v>91857</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>538068</v>
+      </c>
+      <c r="R261" t="n">
+        <v>7202582</v>
+      </c>
+      <c r="S261" t="n">
+        <v>10</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>128891090</v>
+      </c>
+      <c r="B262" t="n">
+        <v>92281</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>717</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Borsttagging</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Gloiodon strigosus</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Schwein. : Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>537943</v>
+      </c>
+      <c r="R262" t="n">
+        <v>7202679</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>128891084</v>
+      </c>
+      <c r="B263" t="n">
+        <v>88754</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>538189</v>
+      </c>
+      <c r="R263" t="n">
+        <v>7202628</v>
+      </c>
+      <c r="S263" t="n">
+        <v>10</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>128891089</v>
+      </c>
+      <c r="B264" t="n">
+        <v>86935</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Handsktummen, Stalon, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>538074</v>
+      </c>
+      <c r="R264" t="n">
+        <v>7202666</v>
+      </c>
+      <c r="S264" t="n">
+        <v>10</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91700</v>
+        <v>91705</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86935</v>
+        <v>86936</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>100719</v>
+        <v>91800</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,6 +29296,21 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29312,32 +29327,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B258" t="n">
-        <v>91795</v>
+        <v>100726</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29408,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29427,7 +29427,7 @@
         <v>128891099</v>
       </c>
       <c r="B259" t="n">
-        <v>90929</v>
+        <v>90934</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>91857</v>
+        <v>91862</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>92281</v>
+        <v>92286</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86935</v>
+        <v>86936</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -29327,10 +29327,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891092</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>100726</v>
+        <v>90934</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29338,21 +29338,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>222771</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>537853</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202655</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29424,10 +29424,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891099</v>
+        <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>90934</v>
+        <v>100726</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29435,21 +29435,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4189</v>
+        <v>222771</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538171</v>
+        <v>537853</v>
       </c>
       <c r="R259" t="n">
-        <v>7202593</v>
+        <v>7202655</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>91862</v>
+        <v>92286</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R261" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>92286</v>
+        <v>91862</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R262" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>91800</v>
+        <v>90934</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R257" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,21 +29296,6 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29327,32 +29312,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B258" t="n">
-        <v>90934</v>
+        <v>91800</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R258" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29408,6 +29393,21 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91705</v>
+        <v>91709</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86936</v>
+        <v>86940</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>128891088</v>
       </c>
       <c r="B255" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,10 +29215,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891099</v>
+        <v>128891092</v>
       </c>
       <c r="B257" t="n">
-        <v>90934</v>
+        <v>100730</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29226,21 +29226,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4189</v>
+        <v>222771</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538171</v>
+        <v>537853</v>
       </c>
       <c r="R257" t="n">
-        <v>7202593</v>
+        <v>7202655</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29312,32 +29312,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>91800</v>
+        <v>90938</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29393,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29424,32 +29409,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B259" t="n">
-        <v>100726</v>
+        <v>91804</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29444,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R259" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29505,6 +29490,21 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>92286</v>
+        <v>91866</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R261" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>91862</v>
+        <v>92290</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R262" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88755</v>
+        <v>88759</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86936</v>
+        <v>86940</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28775,39 +28775,39 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>96882</v>
+        <v>92443</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R253" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28864,21 +28864,6 @@
       <c r="AG253" t="b">
         <v>0</v>
       </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
@@ -28887,39 +28872,39 @@
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>92443</v>
+        <v>96882</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28929,10 +28914,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R254" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28976,6 +28961,21 @@
       <c r="AG254" t="b">
         <v>0</v>
       </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -29208,39 +29208,39 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>100730</v>
+        <v>91804</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29297,6 +29297,21 @@
       <c r="AG257" t="b">
         <v>0</v>
       </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
@@ -29305,7 +29320,7 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
@@ -29402,39 +29417,39 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>91804</v>
+        <v>100730</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29444,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R259" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29491,21 +29506,6 @@
       <c r="AG259" t="b">
         <v>0</v>
       </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
@@ -29611,17 +29611,17 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>91866</v>
+        <v>92290</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R261" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29723,17 +29723,17 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>92290</v>
+        <v>91866</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R262" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28775,39 +28775,39 @@
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>92443</v>
+        <v>96882</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R253" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28864,6 +28864,21 @@
       <c r="AG253" t="b">
         <v>0</v>
       </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
@@ -28872,39 +28887,39 @@
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>96882</v>
+        <v>92443</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28914,10 +28929,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R254" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28961,21 +28976,6 @@
       <c r="AG254" t="b">
         <v>0</v>
       </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
@@ -29208,39 +29208,39 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>91804</v>
+        <v>90938</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R257" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29297,21 +29297,6 @@
       <c r="AG257" t="b">
         <v>0</v>
       </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
@@ -29320,39 +29305,39 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B258" t="n">
-        <v>90938</v>
+        <v>91804</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R258" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29409,6 +29394,21 @@
       <c r="AG258" t="b">
         <v>0</v>
       </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
@@ -29514,7 +29514,7 @@
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
@@ -29723,7 +29723,7 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
@@ -29932,7 +29932,7 @@
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
@@ -30029,7 +30029,7 @@
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91709</v>
+        <v>91714</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86940</v>
+        <v>86945</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>128891088</v>
       </c>
       <c r="B255" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>90938</v>
+        <v>91809</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,6 +29296,21 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29312,32 +29327,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>91804</v>
+        <v>90943</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29408,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29427,7 +29427,7 @@
         <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88759</v>
+        <v>88764</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86940</v>
+        <v>86945</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>96897</v>
+        <v>92456</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R253" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,21 +28863,6 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28894,32 +28879,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>92456</v>
+        <v>96897</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28929,10 +28914,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R254" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28975,6 +28960,21 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86952</v>
+        <v>86955</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>128891092</v>
       </c>
       <c r="B257" t="n">
-        <v>100745</v>
+        <v>100750</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29312,32 +29312,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B258" t="n">
-        <v>90950</v>
+        <v>91808</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R258" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,6 +29393,21 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29409,32 +29424,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B259" t="n">
-        <v>91805</v>
+        <v>90953</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29444,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R259" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29490,21 +29505,6 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>92303</v>
+        <v>92308</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88771</v>
+        <v>88774</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86952</v>
+        <v>86955</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86955</v>
+        <v>86958</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>92461</v>
+        <v>96905</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R253" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,6 +28863,21 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28879,32 +28894,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>96902</v>
+        <v>92464</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28914,10 +28929,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R254" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28960,21 +28975,6 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -28994,7 +28994,7 @@
         <v>128891088</v>
       </c>
       <c r="B255" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>100750</v>
+        <v>91811</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,6 +29296,21 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29312,32 +29327,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>91808</v>
+        <v>90956</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29408,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29424,10 +29424,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891099</v>
+        <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>90953</v>
+        <v>100753</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29435,21 +29435,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4189</v>
+        <v>222771</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538171</v>
+        <v>537853</v>
       </c>
       <c r="R259" t="n">
-        <v>7202593</v>
+        <v>7202655</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>91882</v>
+        <v>92311</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R261" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>92308</v>
+        <v>91885</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R262" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88774</v>
+        <v>88777</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86955</v>
+        <v>86958</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>96905</v>
+        <v>92464</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R253" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,21 +28863,6 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28894,32 +28879,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>92464</v>
+        <v>96905</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28929,10 +28914,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R254" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28975,6 +28960,21 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>91811</v>
+        <v>90956</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R257" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,21 +29296,6 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29327,32 +29312,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B258" t="n">
-        <v>90956</v>
+        <v>91811</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R258" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29408,6 +29393,21 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -30136,7 +30136,7 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>92311</v>
+        <v>91885</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R261" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>91885</v>
+        <v>92311</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R262" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86958</v>
+        <v>86962</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>128891088</v>
       </c>
       <c r="B255" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>90956</v>
+        <v>91818</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,6 +29296,21 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29312,32 +29327,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>91811</v>
+        <v>90960</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29408,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29427,7 +29427,7 @@
         <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>92311</v>
+        <v>92318</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88777</v>
+        <v>88781</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86958</v>
+        <v>86962</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92464</v>
+        <v>92471</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>92471</v>
+        <v>96915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R253" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,6 +28863,21 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28879,32 +28894,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>96915</v>
+        <v>92471</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28914,10 +28929,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R254" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28960,21 +28975,6 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>91818</v>
+        <v>90960</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R257" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,21 +29296,6 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29327,32 +29312,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B258" t="n">
-        <v>90960</v>
+        <v>91818</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R258" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29408,6 +29393,21 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86962</v>
+        <v>86969</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>96915</v>
+        <v>92478</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R253" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,21 +28863,6 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28894,32 +28879,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>92471</v>
+        <v>96922</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28929,10 +28914,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R254" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28975,6 +28960,21 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>90960</v>
+        <v>90967</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29312,32 +29312,32 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B258" t="n">
-        <v>91818</v>
+        <v>100770</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29393,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29424,32 +29409,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B259" t="n">
-        <v>100763</v>
+        <v>91825</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29444,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R259" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29505,6 +29490,21 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>91892</v>
+        <v>92325</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R261" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>92318</v>
+        <v>91899</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R262" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88781</v>
+        <v>88788</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86962</v>
+        <v>86969</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86969</v>
+        <v>86971</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>92478</v>
+        <v>96924</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R253" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,6 +28863,21 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28879,32 +28894,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>96922</v>
+        <v>92480</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28914,10 +28929,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R254" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28960,21 +28975,6 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -28994,7 +28994,7 @@
         <v>128891088</v>
       </c>
       <c r="B255" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>90967</v>
+        <v>90969</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>128891092</v>
       </c>
       <c r="B258" t="n">
-        <v>100770</v>
+        <v>100772</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>128891097</v>
       </c>
       <c r="B259" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88788</v>
+        <v>88790</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86969</v>
+        <v>86971</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92478</v>
+        <v>92480</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>90969</v>
+        <v>91827</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,6 +29296,21 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29312,10 +29327,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891092</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>100772</v>
+        <v>90969</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29323,21 +29338,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>222771</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>537853</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202655</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29409,32 +29424,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>91827</v>
+        <v>100772</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29444,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R259" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29490,21 +29505,6 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91743</v>
+        <v>91752</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86971</v>
+        <v>86972</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>96924</v>
+        <v>92494</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R253" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,21 +28863,6 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28894,32 +28879,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>92480</v>
+        <v>96950</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28929,10 +28914,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R254" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28975,6 +28960,21 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29123,12 +29123,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891097</v>
+        <v>128891099</v>
       </c>
       <c r="B257" t="n">
-        <v>91827</v>
+        <v>90970</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>4189</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538053</v>
+        <v>538171</v>
       </c>
       <c r="R257" t="n">
-        <v>7202582</v>
+        <v>7202593</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29297,21 +29297,6 @@
       <c r="AG257" t="b">
         <v>0</v>
       </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
@@ -29320,39 +29305,39 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Carl Jansson, Isak Vahlström, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B258" t="n">
-        <v>90969</v>
+        <v>91837</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R258" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29408,6 +29393,21 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29427,7 +29427,7 @@
         <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>100772</v>
+        <v>100798</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>92327</v>
+        <v>91910</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R261" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>91901</v>
+        <v>92341</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R262" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88790</v>
+        <v>88791</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86971</v>
+        <v>86972</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28572,7 +28572,7 @@
         <v>128823092</v>
       </c>
       <c r="B251" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>92494</v>
+        <v>96951</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R253" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,6 +28863,21 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28879,32 +28894,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>96950</v>
+        <v>92495</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28914,10 +28929,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R254" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28960,21 +28975,6 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891099</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>90970</v>
+        <v>91838</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4189</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538171</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202593</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29297,6 +29297,21 @@
       <c r="AG257" t="b">
         <v>0</v>
       </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
@@ -29305,39 +29320,39 @@
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Carl Jansson, Isak Vahlström, Elin Kannerby</t>
+          <t>Carl Jansson, Isak Vahlström, Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B258" t="n">
-        <v>91837</v>
+        <v>100799</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29347,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R258" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29393,21 +29408,6 @@
       </c>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
@@ -29424,10 +29424,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891092</v>
+        <v>128891099</v>
       </c>
       <c r="B259" t="n">
-        <v>100798</v>
+        <v>90970</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29435,21 +29435,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222771</v>
+        <v>4189</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>537853</v>
+        <v>538171</v>
       </c>
       <c r="R259" t="n">
-        <v>7202655</v>
+        <v>7202593</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>92341</v>
+        <v>92342</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28785,7 +28785,7 @@
         <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29327,10 +29327,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128891092</v>
+        <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>100799</v>
+        <v>90970</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29338,21 +29338,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>222771</v>
+        <v>4189</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -29362,10 +29362,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>537853</v>
+        <v>538171</v>
       </c>
       <c r="R258" t="n">
-        <v>7202655</v>
+        <v>7202593</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29424,10 +29424,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891099</v>
+        <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>90970</v>
+        <v>100800</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -29435,21 +29435,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4189</v>
+        <v>222771</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538171</v>
+        <v>537853</v>
       </c>
       <c r="R259" t="n">
-        <v>7202593</v>
+        <v>7202655</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28688,7 +28688,7 @@
         <v>128891095</v>
       </c>
       <c r="B252" t="n">
-        <v>86972</v>
+        <v>86975</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B253" t="n">
-        <v>96952</v>
+        <v>92498</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R253" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,21 +28863,6 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28894,32 +28879,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B254" t="n">
-        <v>92495</v>
+        <v>96956</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28929,10 +28914,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R254" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28975,6 +28960,21 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -28994,7 +28994,7 @@
         <v>128891088</v>
       </c>
       <c r="B255" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>128891096</v>
       </c>
       <c r="B256" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B257" t="n">
-        <v>91838</v>
+        <v>100804</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R257" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,21 +29296,6 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29330,7 +29315,7 @@
         <v>128891099</v>
       </c>
       <c r="B258" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -29424,32 +29409,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B259" t="n">
-        <v>100800</v>
+        <v>91841</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29459,10 +29444,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R259" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29505,6 +29490,21 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
@@ -29524,7 +29524,7 @@
         <v>128891086</v>
       </c>
       <c r="B260" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B261" t="n">
-        <v>91911</v>
+        <v>92345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R261" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B262" t="n">
-        <v>92342</v>
+        <v>91914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R262" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>
@@ -29845,7 +29845,7 @@
         <v>128891084</v>
       </c>
       <c r="B263" t="n">
-        <v>88791</v>
+        <v>88794</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>128891089</v>
       </c>
       <c r="B264" t="n">
-        <v>86972</v>
+        <v>86975</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -28782,32 +28782,32 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128891094</v>
+        <v>128891085</v>
       </c>
       <c r="B253" t="n">
-        <v>92498</v>
+        <v>96956</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4769</v>
+        <v>53</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -28817,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>538051</v>
+        <v>538126</v>
       </c>
       <c r="R253" t="n">
-        <v>7202590</v>
+        <v>7202737</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28863,6 +28863,21 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
@@ -28879,32 +28894,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128891085</v>
+        <v>128891094</v>
       </c>
       <c r="B254" t="n">
-        <v>96956</v>
+        <v>92498</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28914,10 +28929,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>538126</v>
+        <v>538051</v>
       </c>
       <c r="R254" t="n">
-        <v>7202737</v>
+        <v>7202590</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28960,21 +28975,6 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
@@ -29215,32 +29215,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128891092</v>
+        <v>128891097</v>
       </c>
       <c r="B257" t="n">
-        <v>100804</v>
+        <v>91841</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -29250,10 +29250,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>537853</v>
+        <v>538053</v>
       </c>
       <c r="R257" t="n">
-        <v>7202655</v>
+        <v>7202582</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29296,6 +29296,21 @@
       </c>
       <c r="AG257" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
@@ -29409,32 +29424,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128891097</v>
+        <v>128891092</v>
       </c>
       <c r="B259" t="n">
-        <v>91841</v>
+        <v>100804</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29444,10 +29459,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>538053</v>
+        <v>537853</v>
       </c>
       <c r="R259" t="n">
-        <v>7202582</v>
+        <v>7202655</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29490,21 +29505,6 @@
       </c>
       <c r="AG259" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
@@ -29618,10 +29618,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128891090</v>
+        <v>128891098</v>
       </c>
       <c r="B261" t="n">
-        <v>92345</v>
+        <v>91914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29629,21 +29629,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>717</v>
+        <v>2062</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Borsttagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Gloiodon strigosus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Schwein. : Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29653,10 +29653,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>537943</v>
+        <v>538068</v>
       </c>
       <c r="R261" t="n">
-        <v>7202679</v>
+        <v>7202582</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29702,17 +29702,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29730,10 +29730,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128891098</v>
+        <v>128891090</v>
       </c>
       <c r="B262" t="n">
-        <v>91914</v>
+        <v>92345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29741,21 +29741,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2062</v>
+        <v>717</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Borsttagging</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Gloiodon strigosus</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein. : Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>538068</v>
+        <v>537943</v>
       </c>
       <c r="R262" t="n">
-        <v>7202582</v>
+        <v>7202679</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29814,17 +29814,17 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT262" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30039,7 +30039,7 @@
         <v>129083440</v>
       </c>
       <c r="B265" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30136,7 +30136,7 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Carl Jansson</t>
+          <t>Carl Jansson, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30136,7 +30136,7 @@
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -27527,7 +27527,7 @@
         <v>0</v>
       </c>
       <c r="AE241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30146,7 +30146,7 @@
         <v>130532886</v>
       </c>
       <c r="B266" t="n">
-        <v>80235</v>
+        <v>80261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30146,7 +30146,7 @@
         <v>130532886</v>
       </c>
       <c r="B266" t="n">
-        <v>80261</v>
+        <v>80263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30146,7 +30146,7 @@
         <v>130532886</v>
       </c>
       <c r="B266" t="n">
-        <v>80263</v>
+        <v>80271</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30146,7 +30146,7 @@
         <v>130532886</v>
       </c>
       <c r="B266" t="n">
-        <v>80271</v>
+        <v>80272</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -30146,7 +30146,7 @@
         <v>130532886</v>
       </c>
       <c r="B266" t="n">
-        <v>80272</v>
+        <v>80273</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96446</v>
+        <v>96617</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96446</v>
+        <v>96617</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96617</v>
+        <v>96618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96617</v>
+        <v>96618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96619</v>
+        <v>96625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96619</v>
+        <v>96625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29408-2022 artfynd.xlsx
+++ b/artfynd/A 29408-2022 artfynd.xlsx
@@ -3062,7 +3062,7 @@
         <v>103934082</v>
       </c>
       <c r="B24" t="n">
-        <v>96625</v>
+        <v>96626</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>103996458</v>
       </c>
       <c r="B25" t="n">
-        <v>96625</v>
+        <v>96626</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
